--- a/data/HMD_Ger_doc.xlsx
+++ b/data/HMD_Ger_doc.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edina\Dropbox\ACLSStudium\FS 2026\Deep Learning\Group project\Topic classification of historical political programs\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{20B583A2-0B66-47A6-8F2B-147F324A5732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEFE22B-B234-4032-B9B9-2C36CE30C977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{33B34591-C994-432D-B86D-789183209CDE}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="186">
   <si>
     <t>doc_title</t>
   </si>
@@ -594,6 +594,9 @@
   </si>
   <si>
     <t>deutschfreiheitliche Partei</t>
+  </si>
+  <si>
+    <t>doc_lan</t>
   </si>
 </sst>
 </file>
@@ -995,1805 +998,2111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E046EB6F-3FEF-4CE6-9992-8BEFD7189E34}">
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:K102"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.6328125" customWidth="1"/>
-    <col min="2" max="2" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.36328125" customWidth="1"/>
-    <col min="4" max="4" width="47.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.6328125" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.36328125" customWidth="1"/>
+    <col min="5" max="5" width="47.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2">
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2">
         <v>1907</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1879</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>1906</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
         <v>1897</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
         <v>1901</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
         <v>1907</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8">
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
         <v>1907</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
         <v>1911</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>26</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10">
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
         <v>1911</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
         <v>1911</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>30</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12">
+      <c r="C12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12">
         <v>1911</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>22</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>1891</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>33</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>1896</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>36</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>1905</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>33</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>1907</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>39</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>1913</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18">
+      <c r="C18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
         <v>1907</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>44</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19">
+      <c r="C19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
         <v>1907</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20">
+      <c r="C20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
         <v>1907</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21">
+      <c r="C21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
         <v>1911</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>50</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22">
+      <c r="C22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
         <v>1911</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23">
+      <c r="C23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
         <v>1911</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24">
+      <c r="C24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
         <v>1911</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25">
+      <c r="C25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
         <v>1911</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="F25" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26">
+      <c r="C26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
         <v>1911</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27">
+      <c r="C27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
         <v>1907</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>58</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28">
+      <c r="C28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
         <v>1907</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>1868</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>61</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30">
+      <c r="C30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
         <v>1897</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>63</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31">
+      <c r="C31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
         <v>1901</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
         <v>66</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>1897</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>68</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>1907</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>71</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>1897</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>73</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>1896</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>66</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>1900</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>66</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>1899</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>77</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>64</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>69</v>
       </c>
-      <c r="H37" t="s">
+      <c r="I37" t="s">
         <v>78</v>
       </c>
-      <c r="I37" t="s">
+      <c r="J37" t="s">
         <v>34</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38">
+      <c r="C38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38">
         <v>1901</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>81</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39">
+      <c r="C39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39">
         <v>1907</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>83</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40">
+      <c r="C40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40">
         <v>1900</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>85</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41">
+      <c r="C41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41">
         <v>1901</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
         <v>68</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42">
+      <c r="C42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42">
         <v>1911</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
         <v>88</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>20</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43">
+      <c r="C43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43">
         <v>1897</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>90</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44">
+      <c r="C44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44">
         <v>1901</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>93</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45">
+      <c r="C45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45">
         <v>1907</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>95</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>20</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46">
+      <c r="C46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46">
         <v>1907</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>61</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>20</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47">
+      <c r="C47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47">
         <v>1907</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>95</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48">
+      <c r="C48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48">
         <v>1907</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>66</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>1882</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>100</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50">
+      <c r="C50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50">
         <v>1897</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
         <v>85</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51">
+      <c r="C51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51">
         <v>1900</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>81</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52">
+      <c r="C52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52">
         <v>1900</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>66</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53">
+      <c r="C53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53">
         <v>1907</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>68</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54">
+      <c r="C54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54">
         <v>1900</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>106</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55">
+      <c r="C55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55">
         <v>1907</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
         <v>109</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56">
+      <c r="C56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56">
         <v>1907</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
         <v>106</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57">
+      <c r="C57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57">
         <v>1911</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>112</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>20</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58">
+      <c r="C58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58">
         <v>1911</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>114</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>20</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59">
+      <c r="C59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59">
         <v>1897</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>116</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>20</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60">
+      <c r="C60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60">
         <v>1900</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
         <v>118</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61">
+      <c r="C61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61">
         <v>1911</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
         <v>95</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>20</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62">
+      <c r="C62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62">
         <v>1911</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
         <v>121</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>20</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63">
+      <c r="C63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63">
         <v>1897</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>123</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64">
+      <c r="C64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64">
         <v>1901</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>125</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65">
+      <c r="C65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65">
         <v>1901</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>127</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>20</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66">
+      <c r="C66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66">
         <v>1907</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>114</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>20</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67">
+      <c r="C67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67">
         <v>1911</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>130</v>
       </c>
-      <c r="E67" t="s">
+      <c r="F67" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>20</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68">
+      <c r="C68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68">
         <v>1897</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>83</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>20</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69">
+      <c r="C69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69">
         <v>1900</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>68</v>
       </c>
-      <c r="E69" t="s">
+      <c r="F69" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>20</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70">
+      <c r="C70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70">
         <v>1907</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>81</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>1888</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>135</v>
       </c>
-      <c r="E71" t="s">
+      <c r="F71" t="s">
         <v>19</v>
       </c>
-      <c r="F71" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
+      <c r="G71" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>20</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>1899</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
         <v>18</v>
       </c>
-      <c r="E72" t="s">
+      <c r="F72" t="s">
         <v>19</v>
       </c>
-      <c r="F72" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>20</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>1901</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>138</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>19</v>
       </c>
-      <c r="F73" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
+      <c r="G73" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74">
+      <c r="C74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74">
         <v>1907</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>140</v>
       </c>
-      <c r="E74" t="s">
+      <c r="F74" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75">
+      <c r="C75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75">
         <v>1911</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
         <v>127</v>
       </c>
-      <c r="E75" t="s">
+      <c r="F75" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76">
+      <c r="C76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76">
         <v>1897</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
         <v>143</v>
       </c>
-      <c r="E76" t="s">
+      <c r="F76" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="3" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>20</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77">
+      <c r="C77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77">
         <v>1900</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>145</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="3" t="s">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78">
+      <c r="C78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78">
         <v>1907</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>66</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79">
+      <c r="C79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79">
         <v>1911</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>148</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>20</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80">
+      <c r="C80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80">
         <v>1897</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>150</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>20</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81">
+      <c r="C81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81">
         <v>1900</v>
       </c>
-      <c r="E81" t="s">
+      <c r="F81" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>20</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82">
+      <c r="C82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82">
         <v>1897</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>153</v>
       </c>
-      <c r="E82" t="s">
+      <c r="F82" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>20</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>1880</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>63</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84">
+      <c r="C84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84">
         <v>1907</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>157</v>
       </c>
-      <c r="E84" t="s">
+      <c r="F84" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>20</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>1899</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
         <v>159</v>
       </c>
-      <c r="E85" t="s">
+      <c r="F85" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="s">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>20</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B86" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C86">
+      <c r="C86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86">
         <v>1897</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
         <v>39</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B87" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C87">
+      <c r="C87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87">
         <v>1900</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
         <v>39</v>
       </c>
-      <c r="E87" t="s">
+      <c r="F87" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="3" t="s">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>20</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C88">
+      <c r="C88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88">
         <v>1900</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E88" t="s">
         <v>164</v>
       </c>
-      <c r="E88" t="s">
+      <c r="F88" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="3" t="s">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>20</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C89">
+      <c r="C89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89">
         <v>1907</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E89" t="s">
         <v>127</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>20</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C90">
+      <c r="C90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90">
         <v>1907</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E90" t="s">
         <v>127</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="3" t="s">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>20</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91">
+      <c r="C91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91">
         <v>1911</v>
       </c>
-      <c r="D91" t="s">
+      <c r="E91" t="s">
         <v>112</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C92">
+      <c r="C92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92">
         <v>1911</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>169</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="s">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>20</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C93">
+      <c r="C93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93">
         <v>1896</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>85</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="3" t="s">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C94">
+      <c r="C94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94">
         <v>1900</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
         <v>172</v>
       </c>
-      <c r="E94" t="s">
+      <c r="F94" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>20</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C95">
+      <c r="C95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95">
         <v>1907</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>174</v>
       </c>
-      <c r="E95" t="s">
+      <c r="F95" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="3" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>20</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C96">
+      <c r="C96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96">
         <v>1911</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>127</v>
       </c>
-      <c r="E96" t="s">
+      <c r="F96" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="3" t="s">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>20</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B97" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C97">
+      <c r="C97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97">
         <v>1900</v>
       </c>
-      <c r="D97" t="s">
+      <c r="E97" t="s">
         <v>83</v>
       </c>
-      <c r="E97" t="s">
+      <c r="F97" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="3" t="s">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>20</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C98">
+      <c r="C98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98">
         <v>1900</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
         <v>81</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" s="3" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C99">
+      <c r="C99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99">
         <v>1900</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
         <v>83</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="3" t="s">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>20</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C100">
+      <c r="C100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100">
         <v>1907</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
         <v>181</v>
       </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="3" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C101">
+      <c r="C101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101">
         <v>1907</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
         <v>81</v>
       </c>
-      <c r="E101" t="s">
+      <c r="F101" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A102" s="3" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>20</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C102">
+      <c r="C102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102">
         <v>1911</v>
       </c>
-      <c r="D102" t="s">
+      <c r="E102" t="s">
         <v>184</v>
       </c>
-      <c r="E102" t="s">
+      <c r="F102" t="s">
         <v>79</v>
       </c>
     </row>
